--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_osierChronicHistopathologicalBehavioral2015.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_osierChronicHistopathologicalBehavioral2015.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{368414A6-7A6E-404D-9DFB-14A4235BCFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D7B3F6-49AD-3345-9A15-4D7B9943EEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35580" yWindow="4580" windowWidth="27640" windowHeight="16940" xr2:uid="{539C4797-CFFF-DC43-AEF8-F097A470AC7F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{539C4797-CFFF-DC43-AEF8-F097A470AC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="104">
   <si>
     <t>Measure</t>
   </si>
@@ -47,301 +47,307 @@
     <t>Subdomain</t>
   </si>
   <si>
+    <t>Motor coordination</t>
+  </si>
+  <si>
+    <t>Sensorimotor asymmetry</t>
+  </si>
+  <si>
+    <t>Sensorimotor coordination</t>
+  </si>
+  <si>
+    <t>Fear conditioning – contextual</t>
+  </si>
+  <si>
+    <t>Fear conditioning – cued</t>
+  </si>
+  <si>
+    <t>% time or entries into open vs. closed arms</t>
+  </si>
+  <si>
+    <t>Ventricular enlargement</t>
+  </si>
+  <si>
+    <t>Macroanatomical structure</t>
+  </si>
+  <si>
+    <t>Gray-matter shrinkage</t>
+  </si>
+  <si>
+    <t>White-matter shrinkage</t>
+  </si>
+  <si>
+    <t>Axonal injury</t>
+  </si>
+  <si>
+    <t>Microanatomical structure</t>
+  </si>
+  <si>
+    <t>Cerebrovascular histopathology</t>
+  </si>
+  <si>
+    <t>Global impairment</t>
+  </si>
+  <si>
+    <t>Fine motor coordination</t>
+  </si>
+  <si>
+    <t>Motor strength/coordination</t>
+  </si>
+  <si>
+    <t>Sensorimotor–tactile integration</t>
+  </si>
+  <si>
+    <t>Rotarod</t>
+  </si>
+  <si>
+    <t>Motor coordination/endurance</t>
+  </si>
+  <si>
+    <t>Spatial learning</t>
+  </si>
+  <si>
+    <t>Morris water maze – probe trial</t>
+  </si>
+  <si>
+    <t>% time in target quadrant</t>
+  </si>
+  <si>
+    <t>Reference memory</t>
+  </si>
+  <si>
+    <t>Passive avoidance</t>
+  </si>
+  <si>
+    <t>Associative (fear) memory</t>
+  </si>
+  <si>
+    <t>Gross contusion volume</t>
+  </si>
+  <si>
+    <t>Volume of cortical lesion by histology or MRI</t>
+  </si>
+  <si>
+    <t>Lateral‐ventricle volume by MRI or section planimetry</t>
+  </si>
+  <si>
+    <t>Regional GM volume or thickness via MRI/VBM or histology</t>
+  </si>
+  <si>
+    <t>WM volume or tract cross-section by MRI-DTI or myelin histology</t>
+  </si>
+  <si>
+    <t>APP or silver staining, DTI fractional anisotropy, axonal bulb counts</t>
+  </si>
+  <si>
+    <t>Myelin integrity</t>
+  </si>
+  <si>
+    <t>Luxol fast blue optical density or EM myelin sheath thickness</t>
+  </si>
+  <si>
+    <t>Microbleed counts, Evans blue extravasation, CD34/VEGF IHC</t>
+  </si>
+  <si>
+    <t>Overall neurological function (m)NSS</t>
+  </si>
+  <si>
+    <t>Composite neuroscore/(m)NSS total (motor, sensory, balance, reflex)</t>
+  </si>
+  <si>
+    <t>Beam balance</t>
+  </si>
+  <si>
+    <t>Time to fall off narrow beam</t>
+  </si>
+  <si>
+    <t>Beam walking</t>
+  </si>
+  <si>
+    <t>Traverse time &amp; foot-slips count</t>
+  </si>
+  <si>
+    <t>Inclined plane</t>
+  </si>
+  <si>
+    <t>Maximal angle maintained</t>
+  </si>
+  <si>
+    <t>Cylinder (limb-use asymmetry)</t>
+  </si>
+  <si>
+    <t>% contacts or rears with impaired vs. unimpaired forelimb</t>
+  </si>
+  <si>
+    <t>Foot-fault</t>
+  </si>
+  <si>
+    <t>Foot-slip/step ratio on grid</t>
+  </si>
+  <si>
+    <t>Adhesive-removal</t>
+  </si>
+  <si>
+    <t>Latency to contact &amp; remove tape from snout or paws</t>
+  </si>
+  <si>
+    <t>Time or rpm at fall from rotating rod</t>
+  </si>
+  <si>
+    <t>Rotating-pole</t>
+  </si>
+  <si>
+    <t>Score (0–6) based on crossing rotating pole &amp; slips</t>
+  </si>
+  <si>
+    <t>Morris water maze – learning latency</t>
+  </si>
+  <si>
+    <t>Escape‐latency across trials</t>
+  </si>
+  <si>
+    <t>Latency to enter shock-paired dark chamber</t>
+  </si>
+  <si>
+    <t>% freezing in original context</t>
+  </si>
+  <si>
+    <t>% freezing to tone in novel context</t>
+  </si>
+  <si>
+    <t>Elevated plus-maze</t>
+  </si>
+  <si>
+    <t>Anxiety-like behavior</t>
+  </si>
+  <si>
+    <t>Cell death – patterns (TUNEL/Hoechst)</t>
+  </si>
+  <si>
+    <t>Molecular &amp; Cellular</t>
+  </si>
+  <si>
+    <t>Apoptosis</t>
+  </si>
+  <si>
+    <t>Apoptosis – caspase-3</t>
+  </si>
+  <si>
+    <t>Cleaved-caspase-3⁺ cell count</t>
+  </si>
+  <si>
+    <t>Autophagy</t>
+  </si>
+  <si>
+    <t>Necrosis</t>
+  </si>
+  <si>
+    <t>Neurogenesis</t>
+  </si>
+  <si>
+    <t>Inflammatory mediators</t>
+  </si>
+  <si>
+    <t>White-matter degeneration (bTBI)</t>
+  </si>
+  <si>
+    <t>Axonal degeneration (bTBI)</t>
+  </si>
+  <si>
+    <t>APP accumulation</t>
+  </si>
+  <si>
+    <t>Vascular tortuosity</t>
+  </si>
+  <si>
+    <t>Hemorrhage (bTBI)</t>
+  </si>
+  <si>
+    <t>Inflammatory/angiogenic mediators</t>
+  </si>
+  <si>
+    <t>Barrier-integrity assay</t>
+  </si>
+  <si>
+    <t>MIF-related protein 8 elevation</t>
+  </si>
+  <si>
+    <t>% TUNEL⁺ cells or % cells with condensed Hoechst-stained nuclei</t>
+  </si>
+  <si>
+    <t>Autophagy – LC3/ATG</t>
+  </si>
+  <si>
+    <t>LC3-II/LC3-I ratio or ATG12–ATG5 conjugate levels by Western blot or IHC</t>
+  </si>
+  <si>
+    <t>Necrosis – H&amp;E</t>
+  </si>
+  <si>
+    <t>Morphological scoring of oncosis, cell swelling and membrane rupture</t>
+  </si>
+  <si>
+    <t>Neurogenesis – BrdU/Ki67/DCX</t>
+  </si>
+  <si>
+    <t>BrdU⁺ and Ki67⁺ proliferating cell counts; DCX⁺ immature neuron counts in DG</t>
+  </si>
+  <si>
+    <t>Cytokine profiling – IL-1β, TNFα, IL-10</t>
+  </si>
+  <si>
+    <t>Tissue cytokine levels by ELISA or IHC</t>
+  </si>
+  <si>
+    <t>Silver staining of degenerating fibers in cerebellar and other WM tracts</t>
+  </si>
+  <si>
+    <t>Amino-silver staining of axonal spheroids and fragmented axons</t>
+  </si>
+  <si>
+    <t>Immunohistochemical detection of amyloid-precursor-protein in axons</t>
+  </si>
+  <si>
+    <t>Myelin loss – Luxol fast blue/MBP IHC (bTBI)</t>
+  </si>
+  <si>
+    <t>Quantification of myelin staining loss on transverse/longitudinal sections</t>
+  </si>
+  <si>
+    <t>Histological assessment of vessel curvature/tortuosity by light microscopy</t>
+  </si>
+  <si>
+    <t>H&amp;E detection and scoring of extravascular blood in defined brain regions</t>
+  </si>
+  <si>
+    <t>Vasculogenesis – VEGF IHC (bTBI)</t>
+  </si>
+  <si>
+    <t>Elevated VEGF⁺ cell counts or signal intensity by IHC in cortex/hippocampus</t>
+  </si>
+  <si>
+    <t>BBB permeability – tracer extravasation (bTBI)</t>
+  </si>
+  <si>
+    <t>Quantification of dye (e.g. Evans blue) or tracer leakage into parenchyma</t>
+  </si>
+  <si>
+    <t>IHC or ELISA quantification of macrophage-inhibiting-factor-8 levels</t>
+  </si>
+  <si>
+    <t>Imaging</t>
+  </si>
+  <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>Physiology</t>
+  </si>
+  <si>
+    <t>Test Name</t>
+  </si>
+  <si>
     <t>Behavioral</t>
-  </si>
-  <si>
-    <t>Motor coordination</t>
-  </si>
-  <si>
-    <t>Sensorimotor asymmetry</t>
-  </si>
-  <si>
-    <t>Sensorimotor coordination</t>
-  </si>
-  <si>
-    <t>Fear conditioning – contextual</t>
-  </si>
-  <si>
-    <t>Fear conditioning – cued</t>
-  </si>
-  <si>
-    <t>% time or entries into open vs. closed arms</t>
-  </si>
-  <si>
-    <t>Test Name / Measure</t>
-  </si>
-  <si>
-    <t>Ventricular enlargement</t>
-  </si>
-  <si>
-    <t>Imaging &amp; Morphology</t>
-  </si>
-  <si>
-    <t>Macroanatomical structure</t>
-  </si>
-  <si>
-    <t>Gray-matter shrinkage</t>
-  </si>
-  <si>
-    <t>White-matter shrinkage</t>
-  </si>
-  <si>
-    <t>Axonal injury</t>
-  </si>
-  <si>
-    <t>Microanatomical structure</t>
-  </si>
-  <si>
-    <t>Cerebrovascular histopathology</t>
-  </si>
-  <si>
-    <t>Global impairment</t>
-  </si>
-  <si>
-    <t>Fine motor coordination</t>
-  </si>
-  <si>
-    <t>Motor strength/coordination</t>
-  </si>
-  <si>
-    <t>Sensorimotor–tactile integration</t>
-  </si>
-  <si>
-    <t>Rotarod</t>
-  </si>
-  <si>
-    <t>Motor coordination/endurance</t>
-  </si>
-  <si>
-    <t>Spatial learning</t>
-  </si>
-  <si>
-    <t>Morris water maze – probe trial</t>
-  </si>
-  <si>
-    <t>% time in target quadrant</t>
-  </si>
-  <si>
-    <t>Reference memory</t>
-  </si>
-  <si>
-    <t>Passive avoidance</t>
-  </si>
-  <si>
-    <t>Associative (fear) memory</t>
-  </si>
-  <si>
-    <t>Gross contusion volume</t>
-  </si>
-  <si>
-    <t>Volume of cortical lesion by histology or MRI</t>
-  </si>
-  <si>
-    <t>Lateral‐ventricle volume by MRI or section planimetry</t>
-  </si>
-  <si>
-    <t>Regional GM volume or thickness via MRI/VBM or histology</t>
-  </si>
-  <si>
-    <t>WM volume or tract cross-section by MRI-DTI or myelin histology</t>
-  </si>
-  <si>
-    <t>APP or silver staining, DTI fractional anisotropy, axonal bulb counts</t>
-  </si>
-  <si>
-    <t>Myelin integrity</t>
-  </si>
-  <si>
-    <t>Luxol fast blue optical density or EM myelin sheath thickness</t>
-  </si>
-  <si>
-    <t>Microbleed counts, Evans blue extravasation, CD34/VEGF IHC</t>
-  </si>
-  <si>
-    <t>Overall neurological function (m)NSS</t>
-  </si>
-  <si>
-    <t>Composite neuroscore/(m)NSS total (motor, sensory, balance, reflex)</t>
-  </si>
-  <si>
-    <t>Beam balance</t>
-  </si>
-  <si>
-    <t>Time to fall off narrow beam</t>
-  </si>
-  <si>
-    <t>Beam walking</t>
-  </si>
-  <si>
-    <t>Traverse time &amp; foot-slips count</t>
-  </si>
-  <si>
-    <t>Inclined plane</t>
-  </si>
-  <si>
-    <t>Maximal angle maintained</t>
-  </si>
-  <si>
-    <t>Cylinder (limb-use asymmetry)</t>
-  </si>
-  <si>
-    <t>% contacts or rears with impaired vs. unimpaired forelimb</t>
-  </si>
-  <si>
-    <t>Foot-fault</t>
-  </si>
-  <si>
-    <t>Foot-slip/step ratio on grid</t>
-  </si>
-  <si>
-    <t>Adhesive-removal</t>
-  </si>
-  <si>
-    <t>Latency to contact &amp; remove tape from snout or paws</t>
-  </si>
-  <si>
-    <t>Time or rpm at fall from rotating rod</t>
-  </si>
-  <si>
-    <t>Rotating-pole</t>
-  </si>
-  <si>
-    <t>Score (0–6) based on crossing rotating pole &amp; slips</t>
-  </si>
-  <si>
-    <t>Morris water maze – learning latency</t>
-  </si>
-  <si>
-    <t>Escape‐latency across trials</t>
-  </si>
-  <si>
-    <t>Latency to enter shock-paired dark chamber</t>
-  </si>
-  <si>
-    <t>% freezing in original context</t>
-  </si>
-  <si>
-    <t>% freezing to tone in novel context</t>
-  </si>
-  <si>
-    <t>Elevated plus-maze</t>
-  </si>
-  <si>
-    <t>Anxiety-like behavior</t>
-  </si>
-  <si>
-    <t>Cell death – patterns (TUNEL/Hoechst)</t>
-  </si>
-  <si>
-    <t>Molecular &amp; Cellular</t>
-  </si>
-  <si>
-    <t>Apoptosis</t>
-  </si>
-  <si>
-    <t>Apoptosis – caspase-3</t>
-  </si>
-  <si>
-    <t>Cleaved-caspase-3⁺ cell count</t>
-  </si>
-  <si>
-    <t>Autophagy</t>
-  </si>
-  <si>
-    <t>Necrosis</t>
-  </si>
-  <si>
-    <t>Neurogenesis</t>
-  </si>
-  <si>
-    <t>Inflammatory mediators</t>
-  </si>
-  <si>
-    <t>White-matter degeneration (bTBI)</t>
-  </si>
-  <si>
-    <t>Axonal degeneration (bTBI)</t>
-  </si>
-  <si>
-    <t>APP accumulation</t>
-  </si>
-  <si>
-    <t>Vascular tortuosity</t>
-  </si>
-  <si>
-    <t>Hemorrhage (bTBI)</t>
-  </si>
-  <si>
-    <t>Inflammatory/angiogenic mediators</t>
-  </si>
-  <si>
-    <t>Barrier-integrity assay</t>
-  </si>
-  <si>
-    <t>MIF-related protein 8 elevation</t>
-  </si>
-  <si>
-    <t>% TUNEL⁺ cells or % cells with condensed Hoechst-stained nuclei</t>
-  </si>
-  <si>
-    <t>Autophagy – LC3/ATG</t>
-  </si>
-  <si>
-    <t>LC3-II/LC3-I ratio or ATG12–ATG5 conjugate levels by Western blot or IHC</t>
-  </si>
-  <si>
-    <t>Necrosis – H&amp;E</t>
-  </si>
-  <si>
-    <t>Morphological scoring of oncosis, cell swelling and membrane rupture</t>
-  </si>
-  <si>
-    <t>Neurogenesis – BrdU/Ki67/DCX</t>
-  </si>
-  <si>
-    <t>BrdU⁺ and Ki67⁺ proliferating cell counts; DCX⁺ immature neuron counts in DG</t>
-  </si>
-  <si>
-    <t>Cytokine profiling – IL-1β, TNFα, IL-10</t>
-  </si>
-  <si>
-    <t>Tissue cytokine levels by ELISA or IHC</t>
-  </si>
-  <si>
-    <t>Silver staining of degenerating fibers in cerebellar and other WM tracts</t>
-  </si>
-  <si>
-    <t>Amino-silver staining of axonal spheroids and fragmented axons</t>
-  </si>
-  <si>
-    <t>Immunohistochemical detection of amyloid-precursor-protein in axons</t>
-  </si>
-  <si>
-    <t>Myelin loss – Luxol fast blue/MBP IHC (bTBI)</t>
-  </si>
-  <si>
-    <t>Quantification of myelin staining loss on transverse/longitudinal sections</t>
-  </si>
-  <si>
-    <t>Histological assessment of vessel curvature/tortuosity by light microscopy</t>
-  </si>
-  <si>
-    <t>H&amp;E detection and scoring of extravascular blood in defined brain regions</t>
-  </si>
-  <si>
-    <t>Vasculogenesis – VEGF IHC (bTBI)</t>
-  </si>
-  <si>
-    <t>Elevated VEGF⁺ cell counts or signal intensity by IHC in cortex/hippocampus</t>
-  </si>
-  <si>
-    <t>BBB permeability – tracer extravasation (bTBI)</t>
-  </si>
-  <si>
-    <t>Quantification of dye (e.g. Evans blue) or tracer leakage into parenchyma</t>
-  </si>
-  <si>
-    <t>IHC or ELISA quantification of macrophage-inhibiting-factor-8 levels</t>
   </si>
 </sst>
 </file>
@@ -739,7 +745,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -753,520 +759,520 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
+        <v>36</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
+        <v>38</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
         <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3</v>
+        <v>46</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
+        <v>50</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
         <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>3</v>
+        <v>24</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3</v>
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
+        <v>78</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
         <v>65</v>
       </c>
+      <c r="C25" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
+        <v>80</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
+        <v>82</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>65</v>
+        <v>84</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>65</v>
+        <v>86</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>12</v>
+        <v>87</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
+        <v>88</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
+        <v>89</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>12</v>
+        <v>91</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" t="s">
-        <v>12</v>
+        <v>92</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
+        <v>93</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" t="s">
-        <v>65</v>
+        <v>95</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>65</v>
+        <v>97</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" t="s">
-        <v>65</v>
+        <v>98</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
